--- a/eval/gold_scenarios/tocs/q1_pass_dc9_02_ref.xlsx
+++ b/eval/gold_scenarios/tocs/q1_pass_dc9_02_ref.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N62"/>
+  <dimension ref="A1:N65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -726,89 +726,35 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Testing procedures</t>
-        </is>
-      </c>
-    </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Design attributes</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>ToC procedures to be performed</t>
-        </is>
-      </c>
-    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Billing total per supporting schedule DC-5.7 (USD)</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>272361</v>
+      </c>
+    </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Del</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Preparer signed off with date on the Checklist.</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Inspect Checklist column F for preparer initials and date.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Del</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Independent reviewer signed off with date.</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Inspect Checklist column G for reviewer initials and date.</t>
-        </is>
-      </c>
-    </row>
+          <t>Testing procedures</t>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Del</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Billing formulas tie to the underlying supporting schedules.</t>
+          <t>Design attributes</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Recompute the billing total from the supporting schedule and tie to the summary.</t>
+          <t>ToC procedures to be performed</t>
         </is>
       </c>
     </row>
@@ -820,17 +766,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Billing rate change is supported by a governing-document amendment.</t>
+          <t>Preparer signed off with date on the Checklist.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Inspect the governing-document file for an amendment matching any rate change.</t>
+          <t>Inspect Checklist column F for preparer initials and date.</t>
         </is>
       </c>
     </row>
@@ -842,17 +788,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Asset additions and retirements appear on the supporting schedule.</t>
+          <t>Independent reviewer signed off with date.</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Compare asset additions and retirements listed on the supporting schedule.</t>
+          <t>Inspect Checklist column G for reviewer initials and date.</t>
         </is>
       </c>
     </row>
@@ -864,296 +810,326 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ownership-share percentages match the supporting reference file.</t>
+          <t>Billing formulas tie to the underlying supporting schedules.</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Recompute ownership-share percentages and agree to the supporting reference file.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42"/>
+          <t>Recompute the billing total from the supporting schedule and tie to the summary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Del</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Billing rate change is supported by a governing-document amendment.</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Inspect the governing-document file for an amendment matching any rate change.</t>
+        </is>
+      </c>
+    </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Result of procedures</t>
-        </is>
-      </c>
-    </row>
-    <row r="44"/>
-    <row r="45">
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Sample item #</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Description of sample item</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Date/period</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>W/P references (if needed)</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
+          <t>Del</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Asset additions and retirements appear on the supporting schedule.</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Compare asset additions and retirements listed on the supporting schedule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Del</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-    </row>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ownership-share percentages match the supporting reference file.</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Recompute ownership-share percentages and agree to the supporting reference file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>Result of procedures</t>
+        </is>
+      </c>
+    </row>
+    <row r="47"/>
+    <row r="48">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Sample item #</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Description of sample item</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Date/period</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>W/P references (if needed)</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>Del</t>
         </is>
       </c>
-      <c r="B46" t="n">
+      <c r="B49" t="n">
         <v>1</v>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Quarterly billing-calculation workpaper</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>Q1 2025</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>DC-4.7</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>Del</t>
         </is>
       </c>
-      <c r="B47" t="n">
+      <c r="B50" t="n">
         <v>2</v>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Quarterly billing-calculation workpaper</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>Q4 2024</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>DC-5.2</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
     </row>
-    <row r="48"/>
-    <row r="49">
-      <c r="B49" t="inlineStr">
+    <row r="51"/>
+    <row r="52">
+      <c r="B52" t="inlineStr">
         <is>
           <t>Tickmark key</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="B50" t="inlineStr">
+    <row r="53">
+      <c r="B53" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>Attribute satisfied without exception</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="B51" t="inlineStr">
+    <row r="54">
+      <c r="B54" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>Attribute satisfied with exception</t>
         </is>
       </c>
     </row>
-    <row r="52"/>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    <row r="55"/>
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>Conclusion</t>
         </is>
       </c>
     </row>
-    <row r="54"/>
-    <row r="55">
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Were exceptions noted during testing?</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Do we have persuasive evidence that the exceptions are random?</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Describe our understanding of the nature and cause of the exceptions</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
+    <row r="57"/>
     <row r="58">
       <c r="B58" t="inlineStr">
         <is>
-          <t>Document how we extended our sample to address the random control exception</t>
+          <t>Were exceptions noted during testing?</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" t="inlineStr">
         <is>
-          <t>Did we identify and test effective compensating controls?</t>
+          <t>Do we have persuasive evidence that the exceptions are random?</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" t="inlineStr">
         <is>
-          <t>Reference the name(s) of the effective compensating control(s)</t>
+          <t>Describe our understanding of the nature and cause of the exceptions</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -1165,7 +1141,7 @@
     <row r="61">
       <c r="B61" t="inlineStr">
         <is>
-          <t>Describe if exceptions are determined to be deficiencies and refer to the deficiency evaluation workpaper</t>
+          <t>Document how we extended our sample to address the random control exception</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -1177,10 +1153,46 @@
     <row r="62">
       <c r="B62" t="inlineStr">
         <is>
+          <t>Did we identify and test effective compensating controls?</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Reference the name(s) of the effective compensating control(s)</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Describe if exceptions are determined to be deficiencies and refer to the deficiency evaluation workpaper</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="inlineStr">
+        <is>
           <t>Operating effectiveness conclusion for the period of reliance</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>Effective</t>
         </is>
@@ -1192,6 +1204,7 @@
     <mergeCell ref="G4:J4"/>
     <mergeCell ref="G2:N2"/>
     <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A36:N36"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="B11:C11"/>
@@ -1200,20 +1213,19 @@
     <mergeCell ref="A16:N16"/>
     <mergeCell ref="D11:N11"/>
     <mergeCell ref="B14:C14"/>
+    <mergeCell ref="A46:N46"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="B13:C13"/>
+    <mergeCell ref="A56:N56"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="G3:N3"/>
     <mergeCell ref="D14:F14"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="A21:N21"/>
-    <mergeCell ref="A33:N33"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A8:N8"/>
-    <mergeCell ref="A53:N53"/>
     <mergeCell ref="G1:N1"/>
-    <mergeCell ref="A43:N43"/>
     <mergeCell ref="E3:F3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
